--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0EB999-B8AE-4492-B853-713DEE758B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B1206-9FB6-42E8-8E48-A94F04DB7F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AHT21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>I2C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -210,6 +206,10 @@
   </si>
   <si>
     <t>不占用串口资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DHT20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -291,8 +291,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -644,127 +644,127 @@
         <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -772,25 +772,25 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B1206-9FB6-42E8-8E48-A94F04DB7F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDDE11A-0628-4502-8258-8FD9EEF0A37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>类别</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,6 +210,10 @@
   </si>
   <si>
     <t>DHT20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂不开发</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -248,7 +252,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +262,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,11 +299,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -581,7 +592,7 @@
     <col min="2" max="2" width="18.640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="14.2109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.78515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="32.2109375" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="2"/>
@@ -610,23 +621,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -647,29 +658,29 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -690,29 +701,29 @@
         <v>27</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -733,7 +744,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -747,49 +758,49 @@
         <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>45</v>
       </c>
     </row>

--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/01_板级硬件资源总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDDE11A-0628-4502-8258-8FD9EEF0A37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F37DF-1A4C-41D3-BB92-49B193D64103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -201,10 +201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>带触摸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不占用串口资源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -214,6 +210,10 @@
   </si>
   <si>
     <t>暂不开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时不使用触屏功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -299,12 +299,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -658,7 +659,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>43</v>
@@ -672,7 +673,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>16</v>
@@ -684,27 +685,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -744,7 +745,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -758,7 +759,7 @@
         <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -801,7 +802,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
